--- a/annual/OLS_Delta_Models_Annual.xlsx
+++ b/annual/OLS_Delta_Models_Annual.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Hedonic_Jevons" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Traditional_Jevons" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Comparison" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Model_Period_Matrix" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30770,4 +30771,2665 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:EW6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS Max 64GB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS Max 256GB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS Max 512GB</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XR 64GB</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XR 256GB</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XR 128GB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS 64GB</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS 256GB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 10 256GB</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 10+ 512GB</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 64GB</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 128GB</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro 64GB</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 256GB</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro Max 64GB</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Find N2 Flip 256GB</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 10+ 256GB</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS 512GB</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 7 Pro 5G 256GB</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 8 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 20 Ultra 128GB</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro Max 128GB</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 mini 128GB</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 64GB</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 128GB</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 256GB</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 mini 256GB</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 mini 64GB</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 8 128GB</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord N10 5G 128GB</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 9 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 9 128GB</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 20 128GB</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord 2 5G 128GB</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord N200 64GB</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord N100 5G 64GB</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 mini 512GB</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 mini 256GB</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 mini 128GB</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 256GB</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 128GB</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 512GB</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro Max 128GB</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 8T 256GB</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno7 Pro 5G 256GB</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Find X5 256GB</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Find X5 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22 128GB</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno7 5G 256GB</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22 Ultra 128GB</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22+ 128GB</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22 256GB</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord 2T 128GB</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno8 5G 128GB</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Xcover 5 64GB</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22 Ultra 256GB</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22+ 256GB</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno8 Pro 5G 256GB</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 10 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Fold 4 256GB</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno8 5G 256GB</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno7 5G 128GB</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Fold 4 512GB</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Flip 4 256GB</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Flip 4 512GB</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 128GB</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 256GB</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 512GB</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Plus 128GB</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro Max 128GB</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Plus 256GB</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Plus 512GB</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 11 256GB</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Xcover 6 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A04 64GB</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A34 256GB</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord CE 3 Lite 256GB</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A24 128GB</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A54 128GB</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S23+ 256GB</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S23 Ultra 256GB</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S23 128GB</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A54 256GB</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S23 256GB</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 10T 5G 256GB</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno10 5G 256GB</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno10 Pro 5G 256GB</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Flip 5 512GB</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Fold 5 512GB</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord N30 5G 128GB</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S24 128GB</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S24 256GB</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 256GB</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 512GB</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 128GB</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Plus 512GB</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Plus 256GB</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Plus 128GB</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Flip 5 256GB</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 12R 256GB</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno11 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno11 F 256GB</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - A60 256GB</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 12 256GB</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S24 Ultra 256GB</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone X 64GB</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S24+ 256GB</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno12 256GB</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno12 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno12 F 4G 256GB</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - A80 256GB</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Fold 5 256GB</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 256GB</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Plus 512GB</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Plus 256GB</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Plus 128GB</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 128GB</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 512GB</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Find X8 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno13 F 4G 256GB</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno13 256GB</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno13 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - A60 128GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>2020→2021</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.2334354534404411</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.2334354534404411</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.2334354534404411</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.2562675864676668</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.2562675864676668</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.2562675864676668</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.2553344633677466</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.2553344633677466</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.3121532888575552</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.3676729262478254</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-0.211742950432986</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.211742950432986</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.3265769841806485</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.211742950432986</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.3265769841806485</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.323984417990566</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.323984417990566</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.3265769841806485</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.323984417990566</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>-0.3676729262478254</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.2553344633677466</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.3840577862611869</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.2291971804601673</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.1355324077723246</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.3343964150836439</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-0.3343964150836439</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.3343964150836439</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.2878265703839182</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.2878265703839182</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.2878265703839182</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.03440006847127908</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.02468404401381546</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.02468404401381546</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.02468404401381546</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.03440006847127908</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.03440006847127908</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-0.0973829116614571</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-0.1259460106484547</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-0.189500379192358</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-0.09678925642117212</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.01897946895487973</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>-0.1674539986314692</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-0.1899032676176041</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>0.01215669269547504</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>-0.353114971198125</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="n">
+        <v>-0.3919895083669102</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-0.353114971198125</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="inlineStr"/>
+      <c r="DK2" t="inlineStr"/>
+      <c r="DL2" t="inlineStr"/>
+      <c r="DM2" t="inlineStr"/>
+      <c r="DN2" t="inlineStr"/>
+      <c r="DO2" t="inlineStr"/>
+      <c r="DP2" t="inlineStr"/>
+      <c r="DQ2" t="inlineStr"/>
+      <c r="DR2" t="inlineStr"/>
+      <c r="DS2" t="inlineStr"/>
+      <c r="DT2" t="inlineStr"/>
+      <c r="DU2" t="inlineStr"/>
+      <c r="DV2" t="inlineStr"/>
+      <c r="DW2" t="inlineStr"/>
+      <c r="DX2" t="inlineStr"/>
+      <c r="DY2" t="inlineStr"/>
+      <c r="DZ2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr"/>
+      <c r="EF2" t="inlineStr"/>
+      <c r="EG2" t="inlineStr"/>
+      <c r="EH2" t="inlineStr"/>
+      <c r="EI2" t="inlineStr"/>
+      <c r="EJ2" t="inlineStr"/>
+      <c r="EK2" t="inlineStr"/>
+      <c r="EL2" t="inlineStr"/>
+      <c r="EM2" t="inlineStr"/>
+      <c r="EN2" t="inlineStr"/>
+      <c r="EO2" t="inlineStr"/>
+      <c r="EP2" t="inlineStr"/>
+      <c r="EQ2" t="inlineStr"/>
+      <c r="ER2" t="inlineStr"/>
+      <c r="ES2" t="inlineStr"/>
+      <c r="ET2" t="inlineStr"/>
+      <c r="EU2" t="inlineStr"/>
+      <c r="EV2" t="inlineStr"/>
+      <c r="EW2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2021→2022</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.3367014245860203</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.3367014245860203</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.3367014245860203</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.2989819417422128</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.2989819417422128</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.2989819417422128</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.3010474439158116</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.3010474439158116</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.3054488931712228</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.2414016220632216</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.3056081339173994</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.3056081339173994</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.3486219092186789</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.3056081339173994</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.3486219092186789</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.3014369056366755</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.3014369056366755</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.3486219092186789</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.3014369056366755</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>-0.2414016220632216</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.3010474439158116</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.3159071543673311</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.276939328482118</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.3223840976965465</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.3952678213295912</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.3952678213295912</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-0.3952678213295912</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.463352898964356</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-0.463352898964356</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.463352898964356</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.2923441991327949</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.4209841656558404</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.4209841656558404</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-0.4209841656558404</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.2923441991327949</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-0.2923441991327949</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.2966538133699376</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-0.2368031638670832</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-0.2749103628110161</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-0.2593921032589195</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.3419194328593601</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.3277744961025402</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-0.150344729392973</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-0.1102393892333534</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-0.2463547369095775</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-0.2463547369095775</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-0.2463547369095775</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-0.3285091730067254</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-0.3285091730067254</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.3285091730067254</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-0.3837552041434215</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-0.2631073724660508</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-0.3837552041434215</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-0.2631073724660508</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-0.3837552041434215</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-0.2631073724660508</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-0.2406506751465399</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-0.4755682305380972</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>-0.3956165415348741</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>-0.3492053244580586</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>-0.2458099489783681</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>-0.4239976799692291</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>-0.1681953689396336</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>-0.1597479954490922</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>-0.2458099489783681</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>-0.3255546297089332</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>-0.4422910398371449</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.06658764869350281</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>-0.1681953689396336</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>-0.2034712781888982</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>-0.5095786820143562</v>
+      </c>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="n">
+        <v>-0.2912933649245069</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>-0.4808413290144302</v>
+      </c>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="n">
+        <v>-0.3350166476643128</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>-0.3337154814359006</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>-0.2899921986960946</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>-0.2932533689752774</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>-0.3369766517150833</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>-0.3369766517150833</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>-0.2177778629200973</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>-0.2448154201364676</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>-0.2203643597013576</v>
+      </c>
+      <c r="CI3" t="inlineStr"/>
+      <c r="CJ3" t="n">
+        <v>-0.2177778629200973</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>-0.1405889732451741</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>-0.1380024764639138</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>-0.1380024764639138</v>
+      </c>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="inlineStr"/>
+      <c r="DI3" t="inlineStr"/>
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="inlineStr"/>
+      <c r="DL3" t="inlineStr"/>
+      <c r="DM3" t="inlineStr"/>
+      <c r="DN3" t="inlineStr"/>
+      <c r="DO3" t="inlineStr"/>
+      <c r="DP3" t="inlineStr"/>
+      <c r="DQ3" t="inlineStr"/>
+      <c r="DR3" t="inlineStr"/>
+      <c r="DS3" t="inlineStr"/>
+      <c r="DT3" t="inlineStr"/>
+      <c r="DU3" t="inlineStr"/>
+      <c r="DV3" t="inlineStr"/>
+      <c r="DW3" t="inlineStr"/>
+      <c r="DX3" t="inlineStr"/>
+      <c r="DY3" t="inlineStr"/>
+      <c r="DZ3" t="inlineStr"/>
+      <c r="EA3" t="inlineStr"/>
+      <c r="EB3" t="inlineStr"/>
+      <c r="EC3" t="inlineStr"/>
+      <c r="ED3" t="inlineStr"/>
+      <c r="EE3" t="inlineStr"/>
+      <c r="EF3" t="inlineStr"/>
+      <c r="EG3" t="inlineStr"/>
+      <c r="EH3" t="inlineStr"/>
+      <c r="EI3" t="inlineStr"/>
+      <c r="EJ3" t="inlineStr"/>
+      <c r="EK3" t="inlineStr"/>
+      <c r="EL3" t="inlineStr"/>
+      <c r="EM3" t="inlineStr"/>
+      <c r="EN3" t="inlineStr"/>
+      <c r="EO3" t="inlineStr"/>
+      <c r="EP3" t="inlineStr"/>
+      <c r="EQ3" t="inlineStr"/>
+      <c r="ER3" t="inlineStr"/>
+      <c r="ES3" t="inlineStr"/>
+      <c r="ET3" t="inlineStr"/>
+      <c r="EU3" t="inlineStr"/>
+      <c r="EV3" t="inlineStr"/>
+      <c r="EW3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2022→2023</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.2309253211865647</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.2309253211865647</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.2309253211865647</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.2825710274802719</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.2825710274802719</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.2825710274802719</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.2956550015466806</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.2956550015466806</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.2390388605401604</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.1765499944311941</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.2396882293516553</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.2396882293516553</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.3322929167699688</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.2396882293516553</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.3322929167699688</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.2971185148607511</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.2971185148607511</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.3322929167699688</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.2971185148607511</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.06372906853759613</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.1765499944311941</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.2956550015466806</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.1352480068582026</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.1716978187488857</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.2619170060721799</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.2225957574239535</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.2225957574239535</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.2225957574239535</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.2509239107070867</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0.2509239107070867</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.2509239107070867</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.238067012587277</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.2383059585962868</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.2383059585962868</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.2383059585962868</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.238067012587277</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.238067012587277</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0.2453944067067415</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-0.3308212176702071</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.188060080420302</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.262223309114731</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.3304484781658099</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.1272438801551881</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-0.2743906401902603</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-0.3463019888872624</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-0.2522870405774797</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-0.2522870405774797</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0.2522870405774797</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.267005348965526</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.267005348965526</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0.267005348965526</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0.2630689815915936</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0.2720418988998903</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0.2630689815915936</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-0.2720418988998903</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0.2630689815915936</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0.2720418988998903</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-0.2074124491344985</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.1283063587884131</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-0.1902155591823183</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-0.1228897472799379</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-0.3230752989508903</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-0.2118821429105573</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>-0.3011190061545357</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-0.3469779720595913</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-0.3230752989508903</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-0.126439915350301</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-0.1960378690437449</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-0.3962846553173468</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-0.3011190061545357</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>-0.3007811516028606</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-0.1078061173120342</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-0.1264212627972951</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-0.1142357068992985</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-0.1010018501982869</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-0.2145245208425539</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-0.06803888644256784</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>-0.1889132212041674</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0.2351100416608981</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>-0.286932707986551</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-0.2407358875298203</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>-0.2407358875298203</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>-0.2520799360176465</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-0.2407099861440947</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.2764995352120102</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>-0.2407099861440947</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>-0.2520799360176465</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>-0.3349789566488148</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0.3105593574544512</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>-0.3105593574544512</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>-0.2407099861440947</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-0.2208309360957227</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>-0.1698878942656647</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>-0.5019219445687502</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>-0.2899411971091552</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>-0.3209614413994955</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>-0.3995614328503795</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>-0.2447003673575793</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>-0.252991035874375</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>-0.4190220649740122</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>-0.3128375240513446</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>-0.1985035469008486</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.3128375240513446</v>
+      </c>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="n">
+        <v>-0.2159424712238627</v>
+      </c>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="n">
+        <v>-0.2170317519384488</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>-0.1214713901432828</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>-0.2913727603092401</v>
+      </c>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="n">
+        <v>-0.2195362571146157</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>-0.2195362571146157</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>-0.2195362571146157</v>
+      </c>
+      <c r="DL4" t="inlineStr"/>
+      <c r="DM4" t="n">
+        <v>-0.2165452710170553</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>-0.2165452710170553</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>-0.3278483167100326</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>-0.2520799360176465</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>-0.2520799360176465</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>-0.3522679159043962</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>-0.3278483167100326</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>-0.1708349314817182</v>
+      </c>
+      <c r="DU4" t="inlineStr"/>
+      <c r="DV4" t="inlineStr"/>
+      <c r="DW4" t="inlineStr"/>
+      <c r="DX4" t="inlineStr"/>
+      <c r="DY4" t="inlineStr"/>
+      <c r="DZ4" t="inlineStr"/>
+      <c r="EA4" t="inlineStr"/>
+      <c r="EB4" t="inlineStr"/>
+      <c r="EC4" t="inlineStr"/>
+      <c r="ED4" t="inlineStr"/>
+      <c r="EE4" t="inlineStr"/>
+      <c r="EF4" t="inlineStr"/>
+      <c r="EG4" t="inlineStr"/>
+      <c r="EH4" t="inlineStr"/>
+      <c r="EI4" t="inlineStr"/>
+      <c r="EJ4" t="inlineStr"/>
+      <c r="EK4" t="inlineStr"/>
+      <c r="EL4" t="inlineStr"/>
+      <c r="EM4" t="inlineStr"/>
+      <c r="EN4" t="inlineStr"/>
+      <c r="EO4" t="inlineStr"/>
+      <c r="EP4" t="inlineStr"/>
+      <c r="EQ4" t="inlineStr"/>
+      <c r="ER4" t="inlineStr"/>
+      <c r="ES4" t="inlineStr"/>
+      <c r="ET4" t="inlineStr"/>
+      <c r="EU4" t="inlineStr"/>
+      <c r="EV4" t="inlineStr"/>
+      <c r="EW4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2023→2024</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.3138978267473332</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.3138978267473332</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.3138978267473332</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.2889297635292906</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.2889297635292906</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.2889297635292906</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.2818200750899723</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.2818200750899723</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.2094495793144588</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.2572292619201259</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.2655452594993583</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.2655452594993583</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.232666013859677</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.2655452594993583</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.232666013859677</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.2585498196387566</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.2585498196387566</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.232666013859677</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.2585498196387566</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.09934249998386391</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.2572292619201259</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.2818200750899723</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.2373012540585743</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.2171293456755378</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.2528538344361244</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.291238308834497</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.291238308834497</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.291238308834497</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.2653921864767403</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0.2653921864767403</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.2653921864767403</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.2391882982222326</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.2458376240961294</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.2458376240961294</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.2458376240961294</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.2391882982222326</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.2391882982222326</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.1663742468636735</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.2228882807372428</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.2082775096596251</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.1626366976633698</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.2054826500238152</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.08126468084477517</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.05591160737400708</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0.09483604983566685</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.2373080866220301</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0.2373080866220301</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0.2373080866220301</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0.2419814576258857</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.2419814576258857</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0.2419814576258857</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-0.2710173430938143</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-0.2797226807771611</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-0.2710173430938143</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0.2797226807771611</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-0.2710173430938143</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-0.2797226807771611</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0.2007073298352571</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-0.0874521444507082</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0.06045976205590622</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0.1123373918468865</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>-0.1890950145714896</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0.1418329337041573</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-0.2536754842925433</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-0.2741145792930624</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-0.1890950145714896</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0.08223542718713173</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>-0.04957730319330531</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>-0.2844270373659964</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>-0.2536754842925433</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-0.2071161426164704</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>-0.09431848150418279</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0.1830514889836841</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>-0.4026274232992701</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>-0.01552886340535467</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0.04188450013892372</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>-0.3356289866226781</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>-0.2325889437099958</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>-0.2995873803865879</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>-0.3247899769932675</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-0.2577915403166754</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0.2577915403166754</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>-0.2913564870923331</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>-0.2677973428458533</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>-0.2748814886480124</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>-0.2677973428458533</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>-0.2913564870923331</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>-0.2540782283909098</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>-0.2705532268352305</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>-0.2705532268352305</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0.2677973428458533</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>-0.2049400004704847</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>-0.2492653548801559</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0.2420364611583412</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>-0.09607915671199466</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0.2432570809552483</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>-0.2232900757733528</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>-0.1150400878319901</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>-0.1242014155698734</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>-0.2978922046253776</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>-0.1763701665294398</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>-0.04804165115539805</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>-0.1763701665294398</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>-0.2859541561021391</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>-0.04063070894845397</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>-0.09403927820329733</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>-0.2890832283301367</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>-0.3938907062180613</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0.1580291892011532</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>-0.1731787242014847</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>-0.1061802875248927</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0.273205624310605</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>-0.273205624310605</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-0.273205624310605</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>-0.2849800337641282</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>-0.2849800337641282</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>-0.2849800337641282</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0.2641703421793203</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>-0.2913564870923331</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>-0.2913564870923331</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>-0.2476953437349996</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>-0.2641703421793203</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>-0.2220847916535446</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>-0.2189557194255471</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>-0.1659751263896902</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>-0.1124828773368288</v>
+      </c>
+      <c r="DX5" t="inlineStr"/>
+      <c r="DY5" t="inlineStr"/>
+      <c r="DZ5" t="n">
+        <v>-0.2367182460029248</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>-0.2018208636139362</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>-0.1880084099185104</v>
+      </c>
+      <c r="EC5" t="inlineStr"/>
+      <c r="ED5" t="inlineStr"/>
+      <c r="EE5" t="n">
+        <v>-0.1162926950217842</v>
+      </c>
+      <c r="EF5" t="inlineStr"/>
+      <c r="EG5" t="n">
+        <v>-0.2598938328648772</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>-0.2633520940258542</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>-0.2639034386078571</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>-0.2881714760920833</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>-0.2881714760920833</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>-0.2913564870923331</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>-0.2881714760920833</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>-0.2639034386078571</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>-0.2474284401635364</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>-0.2633520940258542</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>-0.2633520940258542</v>
+      </c>
+      <c r="ER5" t="inlineStr"/>
+      <c r="ES5" t="n">
+        <v>-0.2913564870923331</v>
+      </c>
+      <c r="ET5" t="inlineStr"/>
+      <c r="EU5" t="inlineStr"/>
+      <c r="EV5" t="inlineStr"/>
+      <c r="EW5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2024→2025</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.1787442751900949</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.1787442751900949</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1787442751900949</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.1817535973101581</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.1817535973101581</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.1817535973101581</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.1805114362790437</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.1805114362790437</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.07420907442501734</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.08307589526402556</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.1719978053948031</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.1719978053948031</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.1693254218157967</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.1719978053948031</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.1693254218157967</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.1797732822270571</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.1797732822270571</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.1693254218157967</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.1797732822270571</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.02801942687243959</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.08307589526402556</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1805114362790437</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.05948015042302353</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.07715451615162908</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.09953898679521309</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.1646249552828362</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.1646249552828362</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.1646249552828362</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.1545723617177261</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.1545723617177261</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.1545723617177261</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.1754101370524818</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.1697218342295694</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.1697218342295694</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0.1697218342295694</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.1754101370524818</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.1754101370524818</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.08189483445802954</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.1396635021020533</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.0802727333738794</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.08832532126771696</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.1033439456338489</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.04149101632007984</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0.04713853450121672</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0.07130878585254602</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.1813809523598959</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.1813809523598959</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0.1813809523598959</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.1817671175344467</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.1817671175344467</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0.1817671175344467</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0.1602883411108484</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.1849624537916478</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-0.1602883411108484</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.1849624537916478</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.1602883411108484</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.1849624537916478</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.08346238117418824</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.03174099268674355</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0.04111565962709948</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0.03654274894882398</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-0.09340300628287465</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0.0935356048581317</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0.1131674532291249</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0.1573639074115249</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-0.09340300628287465</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-0.04122713154153754</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>-0.03768250235224274</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-0.1524234233718556</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0.1131674532291249</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-0.1020462918456918</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0.02850326785627458</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0.1035468663806469</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-0.1164259617779476</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.02086666760570527</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.04144954368441343</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.06110834621211446</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0.06895866469900859</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-0.1242762802648417</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-0.2346146895939846</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-0.1792970740281515</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0.1792970740281515</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0.2054981389487742</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>-0.200202122682414</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>-0.2071139161448316</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>-0.200202122682414</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>-0.2054981389487742</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>-0.2104912007974165</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>-0.208875423601359</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>-0.208875423601359</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-0.200202122682414</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0.09411767959435927</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>-0.07564387786886088</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>-0.1961012712182739</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0.05540092851852603</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0.1709630229096832</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-0.1690343742362919</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0.1161890715224685</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>-0.04747398925389613</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0.1769343304112371</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>-0.09069322958860618</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0.06087145595663539</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>-0.09069322958860618</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>-0.1326876163757473</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>-0.05198565758646295</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0.03116670318895366</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-0.1183752986808096</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>-0.1188009247848282</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.1026373260357953</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>-0.09414831925691214</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-0.03883070369107901</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.1921128472155658</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>-0.1921128472155658</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>-0.1921128472155658</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>-0.2118902386742095</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>-0.2118902386742095</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0.2118902386742095</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.2157856029379709</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0.2054981389487742</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>-0.2054981389487742</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>-0.2174013801340283</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-0.2157856029379709</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>-0.06305768311497646</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0.07737000080991414</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>-0.08477649417532634</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>-0.1059838492595846</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>-0.07113856964804155</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0.04690982692210227</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0.1200334061741503</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.1287973156544836</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>-0.1062466944880352</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>-0.0001014613192299174</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>-0.08477649417532637</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0.1032723470415831</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>-0.07459365931634748</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0.008165693653161998</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>-0.2051415515531627</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>-0.2160975647466734</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.2084351490059035</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>-0.2084351490059035</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>-0.2054981389487742</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>-0.2084351490059035</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>-0.2160975647466734</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>-0.2177133419427308</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0.2051415515531627</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0.2051415515531627</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>-0.03379155912181946</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>-0.2054981389487742</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>-0.01944762346262136</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>-0.07296235516374427</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>-0.06638339807095744</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>-0.07113856964804154</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>